--- a/results/performance_summary.xlsx
+++ b/results/performance_summary.xlsx
@@ -453,17 +453,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>418.73%</t>
+          <t>104.93%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>239.57%</t>
+          <t>65.98%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-32.51%</t>
+          <t>-91.01%</t>
         </is>
       </c>
     </row>
@@ -475,17 +475,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20.49%</t>
+          <t>19.71%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13.03%</t>
+          <t>13.55%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-24.00%</t>
+          <t>-77.25%</t>
         </is>
       </c>
     </row>
@@ -497,17 +497,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>22.13%</t>
+          <t>22.34%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>17.62%</t>
+          <t>16.48%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>99.25%</t>
+          <t>74.22%</t>
         </is>
       </c>
     </row>
@@ -518,13 +518,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="C5" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.24</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="6">
@@ -535,17 +535,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.92%</t>
+          <t>-5.14%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-10.94%</t>
+          <t>-4.35%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-13.53%</t>
+          <t>-19.02%</t>
         </is>
       </c>
     </row>
@@ -557,17 +557,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12.31%</t>
+          <t>5.06%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9.06%</t>
+          <t>5.50%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>92.71%</t>
+          <t>45.30%</t>
         </is>
       </c>
     </row>
@@ -579,17 +579,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-37.03%</t>
+          <t>-26.07%</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-33.72%</t>
+          <t>-24.50%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-78.08%</t>
+          <t>-96.24%</t>
         </is>
       </c>
     </row>
@@ -601,17 +601,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-2.16%</t>
+          <t>-2.29%</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.68%</t>
+          <t>-1.66%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-5.46%</t>
+          <t>-5.66%</t>
         </is>
       </c>
     </row>
@@ -623,17 +623,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-3.28%</t>
+          <t>-3.10%</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.71%</t>
+          <t>-2.40%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-7.26%</t>
+          <t>-9.49%</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>1602</v>
+        <v>888</v>
       </c>
     </row>
     <row r="12">
@@ -659,7 +659,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>43.76%</t>
+          <t>72.86%</t>
         </is>
       </c>
     </row>

--- a/results/performance_summary.xlsx
+++ b/results/performance_summary.xlsx
@@ -425,23 +425,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Meta-Filtered Momentum (No Costs)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Meta-Filtered Momentum (With Costs)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Standard Momentum</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Meta-Filtered Momentum</t>
         </is>
       </c>
     </row>
@@ -453,17 +458,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>555.31%</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>426.97%</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>65.98%</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>104.93%</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>65.98%</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>-91.01%</t>
         </is>
       </c>
     </row>
@@ -475,17 +485,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>60.22%</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>51.70%</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>13.55%</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>19.71%</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>13.55%</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>-77.25%</t>
         </is>
       </c>
     </row>
@@ -497,17 +512,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>27.45%</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>27.41%</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>16.48%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>22.34%</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>16.48%</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>74.22%</t>
         </is>
       </c>
     </row>
@@ -518,13 +538,16 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.88</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-1.04</v>
       </c>
     </row>
     <row r="6">
@@ -535,17 +558,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>-6.27%</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-6.46%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>-4.35%</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>-5.14%</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>-4.35%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>-19.02%</t>
         </is>
       </c>
     </row>
@@ -557,17 +585,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>6.13%</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6.10%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>5.50%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>5.06%</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>5.50%</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>45.30%</t>
         </is>
       </c>
     </row>
@@ -579,17 +612,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>-20.69%</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-23.13%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>-24.50%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>-26.07%</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>-24.50%</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>-96.24%</t>
         </is>
       </c>
     </row>
@@ -601,17 +639,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>-2.53%</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-2.55%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>-1.66%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>-2.29%</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>-1.66%</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>-5.66%</t>
         </is>
       </c>
     </row>
@@ -623,17 +666,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>-3.74%</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-3.79%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>-2.40%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>-3.10%</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>-2.40%</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>-9.49%</t>
         </is>
       </c>
     </row>
@@ -643,11 +691,14 @@
           <t>Trade Count</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="n">
-        <v>888</v>
-      </c>
+      <c r="B11" t="n">
+        <v>2276</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2276</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -655,13 +706,131 @@
           <t>Win Rate</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>72.86%</t>
-        </is>
-      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>39.94%</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>39.94%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Turnover</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>218.6310493830005</v>
+      </c>
+      <c r="C13" t="n">
+        <v>218.6310493830005</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>TP Trades</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>909</v>
+      </c>
+      <c r="C14" t="n">
+        <v>909</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>SL Trades</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1367</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1367</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Time Barrier Trades</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3010</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3010</v>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Avg Holding Period (days)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="C17" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Avg PnL per Trade</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.24%</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Exposure-Weighted Win Rate</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>17.09%</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>17.09%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/performance_summary.xlsx
+++ b/results/performance_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,12 +458,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>555.31%</t>
+          <t>158878.16%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>426.97%</t>
+          <t>76442.90%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -485,12 +485,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.22%</t>
+          <t>534.93%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>51.70%</t>
+          <t>428.60%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -512,12 +512,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>27.45%</t>
+          <t>28.31%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>27.41%</t>
+          <t>28.18%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -534,73 +534,81 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Sharpe Ratio</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.88</v>
+          <t>Semi-volatility</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>15.06%</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>15.26%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>11.73%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>14.72%</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Minimum Return</t>
+          <t>Sharpe Ratio</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-6.27%</t>
+          <t>18.90</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-6.46%</t>
+          <t>15.21</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-4.35%</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-5.14%</t>
+          <t>0.88</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Maximum Return</t>
+          <t>Sortino Ratio</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6.13%</t>
+          <t>35.52</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6.10%</t>
+          <t>28.08</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.50%</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5.06%</t>
+          <t>1.34</t>
         </is>
       </c>
     </row>
@@ -612,12 +620,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-20.69%</t>
+          <t>-9.46%</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-23.13%</t>
+          <t>-10.81%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -634,27 +642,27 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Value at Risk (VaR)</t>
+          <t>Avg Drawdown</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-2.53%</t>
+          <t>-1.10%</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.55%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-1.66%</t>
+          <t>-6.12%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-2.29%</t>
+          <t>-7.13%</t>
         </is>
       </c>
     </row>
@@ -666,12 +674,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-3.74%</t>
+          <t>-2.87%</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.79%</t>
+          <t>-2.96%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -688,108 +696,180 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Trade Count</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2276</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2276</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.297</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.264</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-0.204</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-0.188</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Win Rate</t>
+          <t>Kurtosis</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>39.94%</t>
+          <t>0.385</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>39.94%</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+          <t>0.405</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.927</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0.652</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Turnover</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>218.6310493830005</v>
-      </c>
-      <c r="C13" t="n">
-        <v>218.6310493830005</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+          <t>Correlation to SPY</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>-0.011</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-0.009</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.825</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>TP Trades</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>909</v>
-      </c>
-      <c r="C14" t="n">
-        <v>909</v>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+          <t>Std Dev Correlation</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0.479</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.479</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0.113</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SL Trades</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1367</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1367</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.897</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1.712</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-0.000</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.048</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Time Barrier Trades</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>3010</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3010</v>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>-0.019</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-0.016</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.118</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Avg Holding Period (days)</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="C17" t="n">
-        <v>7.33</v>
+          <t>Avg Leverage (Gross)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
@@ -797,17 +877,17 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Avg PnL per Trade</t>
+          <t>Max Leverage (Gross)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -816,21 +896,268 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Exposure-Weighted Win Rate</t>
+          <t>Avg Net Exposure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17.09%</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>17.09%</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Trade Count</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>8347</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>8347</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Win Rate</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>62.20%</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>62.20%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Avg Daily Turnover</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>TP Trades</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1865</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1865</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>SL Trades</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2328</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2328</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Timeout / No Signal</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>4154</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4154</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Avg Holding Period (days)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>11.58</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>11.58</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Notional-Weighted Win Rate</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>60.47%</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>60.47%</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Avg PnL per Trade</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0.26%</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0.26%</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Median PnL per Trade</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0.11%</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0.11%</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Long Hit Rate</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>22.34%</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>22.34%</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Short Hit Rate</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/performance_summary.xlsx
+++ b/results/performance_summary.xlsx
@@ -425,18 +425,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Meta-Filtered Momentum (No Costs)</t>
+          <t>Stacked MLP Meta-Labeling (No Costs)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Meta-Filtered Momentum (With Costs)</t>
+          <t>Stacked MLP Meta-Labeling (With Costs)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -447,168 +447,203 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Standard Momentum</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Standard Momentum (Long Short)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Cumulative Return</t>
+          <t>Annualized Return</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>158878.16%</t>
+          <t>39.48%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>76442.90%</t>
+          <t>20.78%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>65.98%</t>
+          <t>25.64%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>104.93%</t>
+          <t>23.69%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Annualized Return</t>
+          <t>Annualized Vol</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>534.93%</t>
+          <t>19.16%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>428.60%</t>
+          <t>19.11%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13.55%</t>
+          <t>12.81%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19.71%</t>
+          <t>17.71%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>9.57%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Annualized Vol</t>
+          <t>Semi-volatility</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>28.31%</t>
+          <t>11.17%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>28.18%</t>
+          <t>11.46%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16.48%</t>
+          <t>8.75%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>22.34%</t>
+          <t>11.46%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>6.45%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Semi-volatility</t>
+          <t>Sharpe Ratio</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15.06%</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15.26%</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11.73%</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14.72%</t>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.09</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Sharpe Ratio</t>
+          <t>Sortino Ratio</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18.90</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15.21</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.13</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Sortino Ratio</t>
+          <t>Conditional VaR (CVaR)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>-2.30%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>-2.38%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-2.34%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-1.38%</t>
         </is>
       </c>
     </row>
@@ -620,22 +655,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-9.46%</t>
+          <t>-13.39%</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-10.81%</t>
+          <t>-18.35%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-24.50%</t>
+          <t>-9.97%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-26.07%</t>
+          <t>-14.02%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-10.21%</t>
         </is>
       </c>
     </row>
@@ -647,49 +687,59 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-1.10%</t>
+          <t>-3.72%</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-5.59%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-6.12%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-7.13%</t>
+          <t>-2.91%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-3.27%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Conditional VaR (CVaR)</t>
+          <t>Max Drawdown Duration (days)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-2.87%</t>
+          <t>101</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.96%</t>
+          <t>196</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-2.40%</t>
+          <t>85</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-3.10%</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>215</t>
         </is>
       </c>
     </row>
@@ -701,22 +751,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>0.122</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>0.064</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.204</t>
+          <t>-0.258</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.188</t>
+          <t>-0.185</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-0.260</t>
         </is>
       </c>
     </row>
@@ -728,20 +783,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.385</t>
+          <t>0.113</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.405</t>
+          <t>0.061</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.927</t>
+          <t>0.736</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
+        <is>
+          <t>0.565</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>0.652</t>
         </is>
@@ -755,12 +815,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-0.011</t>
+          <t>0.116</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.009</t>
+          <t>0.122</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -770,24 +830,29 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.825</t>
+          <t>0.838</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-0.073</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Std Dev Correlation</t>
+          <t>Alpha</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.479</t>
+          <t>0.310</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.479</t>
+          <t>0.164</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -797,367 +862,350 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>-0.046</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Alpha</t>
+          <t>Beta</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.897</t>
+          <t>0.174</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.712</t>
+          <t>0.183</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>1.159</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-0.054</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Beta</t>
+          <t>Positive Months</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-0.019</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.016</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.118</t>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Avg Leverage (Gross)</t>
+          <t>Negative Months</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Max Leverage (Gross)</t>
+          <t>Trade Count</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Avg Net Exposure</t>
+          <t>Win Rate</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>42.81%</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>42.81%</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Trade Count</t>
+          <t>TP Trades</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>564</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>564</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Win Rate</t>
+          <t>SL Trades</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>62.20%</t>
+          <t>395</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>62.20%</t>
+          <t>395</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Avg Daily Turnover</t>
+          <t>Timeout / No Signal</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>321</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>321</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>TP Trades</t>
+          <t>Avg Holding Period (days)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>SL Trades</t>
+          <t>Notional-Weighted Win Rate</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2328</t>
+          <t>41.34%</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2328</t>
+          <t>41.34%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Timeout / No Signal</t>
+          <t>Avg PnL per Trade</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Avg Holding Period (days)</t>
+          <t>Median PnL per Trade</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Notional-Weighted Win Rate</t>
+          <t>Profit Factor</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>60.47%</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>60.47%</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Avg PnL per Trade</t>
+          <t>Long Hit Rate</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>14.29%</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>14.29%</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Median PnL per Trade</t>
+          <t>Short Hit Rate</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>30.56%</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>30.56%</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2.39</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2.39</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>Long Hit Rate</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>22.34%</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>22.34%</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>Short Hit Rate</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/performance_summary.xlsx
+++ b/results/performance_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,12 +431,12 @@
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Stacked MLP Meta-Labeling (No Costs)</t>
+          <t>Stacked MLP Meta-Labeling (Gross)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Stacked MLP Meta-Labeling (With Costs)</t>
+          <t>Stacked MLP Meta-Labeling (Net)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -463,12 +463,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>39.48%</t>
+          <t>67.17%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20.78%</t>
+          <t>50.63%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -495,12 +495,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19.16%</t>
+          <t>19.37%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19.11%</t>
+          <t>19.28%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -527,12 +527,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11.17%</t>
+          <t>12.94%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11.46%</t>
+          <t>13.28%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -559,12 +559,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -591,12 +591,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -623,12 +623,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-2.30%</t>
+          <t>-2.51%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>-2.59%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -655,12 +655,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-13.39%</t>
+          <t>-11.75%</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-18.35%</t>
+          <t>-12.68%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -687,12 +687,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-3.72%</t>
+          <t>-2.95%</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-5.59%</t>
+          <t>-3.83%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>75</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>144</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -751,12 +751,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.020</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>-0.069</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>0.893</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0.882</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.541</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.540</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -847,12 +847,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.310</t>
+          <t>0.339</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>0.236</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>0.818</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>0.813</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -911,12 +911,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -975,12 +975,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -995,12 +995,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>42.81%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>42.81%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>41.34%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>41.34%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14.29%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>14.29%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>30.56%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>30.56%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>

--- a/results/performance_summary.xlsx
+++ b/results/performance_summary.xlsx
@@ -463,27 +463,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>67.17%</t>
+          <t>87.74%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>50.63%</t>
+          <t>69.25%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>25.64%</t>
+          <t>14.48%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23.69%</t>
+          <t>30.15%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>2.70%</t>
         </is>
       </c>
     </row>
@@ -495,27 +495,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19.37%</t>
+          <t>18.95%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19.28%</t>
+          <t>18.94%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12.81%</t>
+          <t>20.99%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17.71%</t>
+          <t>27.92%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.57%</t>
+          <t>13.82%</t>
         </is>
       </c>
     </row>
@@ -527,27 +527,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12.94%</t>
+          <t>11.37%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13.28%</t>
+          <t>11.60%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8.75%</t>
+          <t>17.16%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11.46%</t>
+          <t>21.10%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>6.45%</t>
+          <t>10.77%</t>
         </is>
       </c>
     </row>
@@ -559,27 +559,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.20</t>
         </is>
       </c>
     </row>
@@ -591,27 +591,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.25</t>
         </is>
       </c>
     </row>
@@ -623,27 +623,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-2.51%</t>
+          <t>-2.29%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.59%</t>
+          <t>-2.35%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>-3.20%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>-3.99%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>-2.05%</t>
         </is>
       </c>
     </row>
@@ -655,27 +655,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-11.75%</t>
+          <t>-18.83%</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-12.68%</t>
+          <t>-22.41%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-9.97%</t>
+          <t>-33.72%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-14.02%</t>
+          <t>-37.32%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-10.21%</t>
+          <t>-24.11%</t>
         </is>
       </c>
     </row>
@@ -687,27 +687,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-2.99%</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.83%</t>
+          <t>-3.74%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-1.68%</t>
+          <t>-6.25%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-2.91%</t>
+          <t>-5.74%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-3.27%</t>
+          <t>-9.89%</t>
         </is>
       </c>
     </row>
@@ -719,27 +719,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>136</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>488</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>518</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>1114</t>
         </is>
       </c>
     </row>
@@ -751,27 +751,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.020</t>
+          <t>0.156</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.069</t>
+          <t>0.117</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.258</t>
+          <t>-0.544</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.185</t>
+          <t>-0.405</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.260</t>
+          <t>-1.088</t>
         </is>
       </c>
     </row>
@@ -783,27 +783,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.893</t>
+          <t>0.551</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.882</t>
+          <t>0.566</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.736</t>
+          <t>11.511</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.565</t>
+          <t>7.458</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.652</t>
+          <t>10.098</t>
         </is>
       </c>
     </row>
@@ -815,12 +815,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.541</t>
+          <t>-0.076</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.540</t>
+          <t>-0.073</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -830,12 +830,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.838</t>
+          <t>0.848</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.073</t>
+          <t>-0.116</t>
         </is>
       </c>
     </row>
@@ -847,27 +847,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>0.659</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>0.555</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-0.046</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>0.048</t>
         </is>
       </c>
     </row>
@@ -879,12 +879,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>-0.068</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.813</t>
+          <t>-0.066</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.159</t>
+          <t>1.128</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-0.054</t>
+          <t>-0.076</t>
         </is>
       </c>
     </row>
@@ -911,27 +911,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -943,27 +943,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8552</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8552</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -995,12 +995,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>54.34%</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>54.34%</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2496</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2496</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1774</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1774</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4282</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4282</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>52.93%</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>52.93%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>39.22%</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>39.22%</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>20.73%</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>20.73%</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>

--- a/results/performance_summary.xlsx
+++ b/results/performance_summary.xlsx
@@ -463,12 +463,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>87.74%</t>
+          <t>-10.32%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>69.25%</t>
+          <t>-13.91%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -495,12 +495,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18.95%</t>
+          <t>16.38%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18.94%</t>
+          <t>16.46%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -527,12 +527,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11.37%</t>
+          <t>22.02%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11.60%</t>
+          <t>22.18%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -559,12 +559,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -591,12 +591,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -623,12 +623,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-2.29%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-2.91%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -655,12 +655,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-18.83%</t>
+          <t>-85.71%</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-22.41%</t>
+          <t>-91.47%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -687,12 +687,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-2.99%</t>
+          <t>-16.11%</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.74%</t>
+          <t>-17.45%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>976</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>976</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -751,12 +751,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>0.608</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>0.471</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>51.992</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.566</t>
+          <t>51.474</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-0.076</t>
+          <t>0.283</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.073</t>
+          <t>0.283</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -847,12 +847,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.659</t>
+          <t>-0.347</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.555</t>
+          <t>-0.469</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-0.068</t>
+          <t>0.383</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.066</t>
+          <t>0.384</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -911,12 +911,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -975,12 +975,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8552</t>
+          <t>16211</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>8552</t>
+          <t>16211</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -995,12 +995,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>54.34%</t>
+          <t>53.71%</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>54.34%</t>
+          <t>53.71%</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2496</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2496</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1774</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1774</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>52.93%</t>
+          <t>53.83%</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>52.93%</t>
+          <t>53.83%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.02%</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.02%</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>39.22%</t>
+          <t>47.11%</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>39.22%</t>
+          <t>47.11%</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20.73%</t>
+          <t>40.09%</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20.73%</t>
+          <t>40.09%</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>

--- a/results/performance_summary.xlsx
+++ b/results/performance_summary.xlsx
@@ -473,22 +473,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8.01%</t>
+          <t>9.15%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>3.60%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9.67%</t>
+          <t>10.22%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5.09%</t>
+          <t>6.06%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -515,22 +515,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20.01%</t>
+          <t>19.59%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20.02%</t>
+          <t>19.60%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13.27%</t>
+          <t>13.19%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19.75%</t>
+          <t>19.35%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -557,22 +557,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16.75%</t>
+          <t>15.90%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16.71%</t>
+          <t>15.87%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10.37%</t>
+          <t>10.13%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16.33%</t>
+          <t>15.49%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -599,22 +599,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -641,22 +641,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -683,22 +683,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-3.14%</t>
+          <t>-3.02%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.16%</t>
+          <t>-3.04%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-1.99%</t>
+          <t>-1.97%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-3.11%</t>
+          <t>-2.99%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -725,22 +725,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-32.13%</t>
+          <t>-27.90%</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-33.16%</t>
+          <t>-29.83%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-30.33%</t>
+          <t>-28.45%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-36.30%</t>
+          <t>-32.05%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -767,22 +767,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-10.38%</t>
+          <t>-8.53%</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-13.57%</t>
+          <t>-11.42%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-4.25%</t>
+          <t>-3.96%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-11.65%</t>
+          <t>-9.81%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -809,22 +809,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>492</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>193</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>422</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -851,22 +851,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-1.091</t>
+          <t>-0.846</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.093</t>
+          <t>-0.847</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.781</t>
+          <t>-0.650</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-1.151</t>
+          <t>-0.899</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -893,22 +893,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10.721</t>
+          <t>7.814</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10.698</t>
+          <t>7.801</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6.375</t>
+          <t>5.141</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>9.330</t>
+          <t>6.674</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -935,22 +935,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-0.163</t>
+          <t>-0.157</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.162</t>
+          <t>-0.156</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>0.680</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -977,22 +977,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.130</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>0.078</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>0.039</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>0.078</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1019,22 +1019,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-0.156</t>
+          <t>-0.146</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.155</t>
+          <t>-0.146</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>0.427</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1103,22 +1103,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5724</t>
+          <t>5672</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5724</t>
+          <t>5672</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>61.69%</t>
+          <t>60.54%</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>61.69%</t>
+          <t>60.54%</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>632</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>632</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>62.24%</t>
+          <t>60.15%</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>62.24%</t>
+          <t>60.15%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>55.06%</t>
+          <t>56.18%</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>55.06%</t>
+          <t>56.18%</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>48.98%</t>
+          <t>47.43%</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>48.98%</t>
+          <t>47.43%</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">

--- a/results/performance_summary.xlsx
+++ b/results/performance_summary.xlsx
@@ -473,22 +473,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9.15%</t>
+          <t>16.74%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.60%</t>
+          <t>12.17%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10.22%</t>
+          <t>14.64%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6.06%</t>
+          <t>14.20%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -515,22 +515,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19.59%</t>
+          <t>19.50%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19.60%</t>
+          <t>19.51%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13.19%</t>
+          <t>13.43%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19.35%</t>
+          <t>19.36%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -557,22 +557,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15.90%</t>
+          <t>15.14%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15.87%</t>
+          <t>15.13%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10.13%</t>
+          <t>10.17%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15.49%</t>
+          <t>14.92%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -599,22 +599,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -641,22 +641,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -683,22 +683,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-3.02%</t>
+          <t>-2.95%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.04%</t>
+          <t>-2.97%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-2.00%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-2.99%</t>
+          <t>-2.94%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -725,22 +725,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-27.90%</t>
+          <t>-27.32%</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-29.83%</t>
+          <t>-28.07%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-28.45%</t>
+          <t>-28.07%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-32.05%</t>
+          <t>-30.60%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -767,22 +767,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-8.53%</t>
+          <t>-6.07%</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-11.42%</t>
+          <t>-7.05%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-3.96%</t>
+          <t>-4.14%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-9.81%</t>
+          <t>-6.82%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -809,22 +809,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>297</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>305</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>211</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>301</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -851,22 +851,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-0.846</t>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.847</t>
+          <t>-0.702</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.650</t>
+          <t>-0.553</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.899</t>
+          <t>-0.729</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -893,22 +893,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7.814</t>
+          <t>4.657</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>7.801</t>
+          <t>4.647</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5.141</t>
+          <t>3.803</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6.674</t>
+          <t>4.147</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -935,22 +935,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-0.157</t>
+          <t>-0.122</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.156</t>
+          <t>-0.121</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.680</t>
+          <t>0.693</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -977,22 +977,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.130</t>
+          <t>0.192</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>0.152</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>0.076</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>0.152</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1019,22 +1019,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-0.146</t>
+          <t>-0.113</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.146</t>
+          <t>-0.113</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>0.444</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1103,22 +1103,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>60.54%</t>
+          <t>65.75%</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>60.54%</t>
+          <t>65.75%</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>389</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>389</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>60.15%</t>
+          <t>65.81%</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>60.15%</t>
+          <t>65.81%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>56.18%</t>
+          <t>57.43%</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>56.18%</t>
+          <t>57.43%</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>47.43%</t>
+          <t>61.29%</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>47.43%</t>
+          <t>61.29%</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">

--- a/results/performance_summary.xlsx
+++ b/results/performance_summary.xlsx
@@ -473,22 +473,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8.01%</t>
+          <t>16.74%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>12.17%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9.67%</t>
+          <t>14.64%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5.09%</t>
+          <t>14.20%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -515,22 +515,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20.01%</t>
+          <t>19.50%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20.02%</t>
+          <t>19.51%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13.27%</t>
+          <t>13.43%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19.75%</t>
+          <t>19.36%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -557,22 +557,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16.75%</t>
+          <t>15.14%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16.71%</t>
+          <t>15.13%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10.37%</t>
+          <t>10.17%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16.33%</t>
+          <t>14.92%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -599,22 +599,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>0.73</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0.26</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -641,22 +641,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -683,22 +683,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-3.14%</t>
+          <t>-2.95%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.16%</t>
+          <t>-2.97%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-1.99%</t>
+          <t>-2.00%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-3.11%</t>
+          <t>-2.94%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -725,22 +725,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-32.13%</t>
+          <t>-27.32%</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-33.16%</t>
+          <t>-28.07%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-30.33%</t>
+          <t>-28.07%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-36.30%</t>
+          <t>-30.60%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -767,22 +767,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-10.38%</t>
+          <t>-6.07%</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-13.57%</t>
+          <t>-7.05%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-4.25%</t>
+          <t>-4.14%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-11.65%</t>
+          <t>-6.82%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -809,22 +809,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>297</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>305</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>211</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>301</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -851,22 +851,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-1.091</t>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.093</t>
+          <t>-0.702</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.781</t>
+          <t>-0.553</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-1.151</t>
+          <t>-0.729</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -893,22 +893,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10.721</t>
+          <t>4.657</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10.698</t>
+          <t>4.647</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6.375</t>
+          <t>3.803</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>9.330</t>
+          <t>4.147</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -935,17 +935,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-0.163</t>
+          <t>-0.122</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.162</t>
+          <t>-0.121</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>0.693</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -977,22 +977,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.192</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>0.152</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>0.076</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>0.152</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1019,17 +1019,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-0.156</t>
+          <t>-0.113</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.155</t>
+          <t>-0.113</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>0.444</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1103,22 +1103,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5724</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5724</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>61.69%</t>
+          <t>65.75%</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>61.69%</t>
+          <t>65.75%</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>389</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>389</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>62.24%</t>
+          <t>65.81%</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>62.24%</t>
+          <t>65.81%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>55.06%</t>
+          <t>57.43%</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>55.06%</t>
+          <t>57.43%</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>48.98%</t>
+          <t>61.29%</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>48.98%</t>
+          <t>61.29%</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
